--- a/tailieu/SO_TAY_KTV.xlsx
+++ b/tailieu/SO_TAY_KTV.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\sotay_ktv\sotay_ktv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\sotayFPT_ktv\tailieu\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>Triển khai dịch vụ Internet</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>Bán hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -514,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.5546875" bestFit="1" customWidth="1"/>
@@ -653,6 +656,15 @@
         <v>26</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B13" s="1"/>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B14" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tailieu/SO_TAY_KTV.xlsx
+++ b/tailieu/SO_TAY_KTV.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>Triển khai dịch vụ Internet</t>
   </si>
@@ -161,7 +161,10 @@
     <t>Bán hàng</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>iohaiohhho</t>
   </si>
 </sst>
 </file>
@@ -657,9 +660,14 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="1"/>
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">

--- a/tailieu/SO_TAY_KTV.xlsx
+++ b/tailieu/SO_TAY_KTV.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>Triển khai dịch vụ Internet</t>
   </si>
@@ -159,12 +159,6 @@
   </si>
   <si>
     <t>Bán hàng</t>
-  </si>
-  <si>
-    <t>hello</t>
-  </si>
-  <si>
-    <t>iohaiohhho</t>
   </si>
 </sst>
 </file>
@@ -660,15 +654,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
+      <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="1"/>
